--- a/rapporten/prijsrapport-NL-2026-05-19.xlsx
+++ b/rapporten/prijsrapport-NL-2026-05-19.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="133">
   <si>
     <t>Product</t>
   </si>
@@ -406,46 +406,10 @@
     <t>6291012000261</t>
   </si>
   <si>
-    <t>Hello Kitty Mermaid Parfum set 6 stuks voor kinderen - 6x15ml - Meisjes</t>
-  </si>
-  <si>
-    <t>8721055493105</t>
-  </si>
-  <si>
-    <t>NG Dark Elixir Men Eau de Toilette 100 ml</t>
-  </si>
-  <si>
-    <t>8719214757229</t>
-  </si>
-  <si>
     <t>Azira - Dream Oasis - Eau de Parfum Unisex</t>
   </si>
   <si>
     <t>8721349102706</t>
-  </si>
-  <si>
-    <t>Street Looks Miss Important Eau de Parfum 100ml</t>
-  </si>
-  <si>
-    <t>8715658340287</t>
-  </si>
-  <si>
-    <t>De La Mare Parfum Raggio Di Sole 49 Caramel &amp; Pistachio Eau de Parfum 100 ml</t>
-  </si>
-  <si>
-    <t>8721055498155</t>
-  </si>
-  <si>
-    <t>NG Touch! / Eau de parfum / 80 ml</t>
-  </si>
-  <si>
-    <t>8718421831555</t>
-  </si>
-  <si>
-    <t>NG - Phenom - Eau de Parfum 100ml voor dames</t>
-  </si>
-  <si>
-    <t>8719214753641</t>
   </si>
 </sst>
 </file>
@@ -837,7 +801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -2418,177 +2382,21 @@
         <v>132</v>
       </c>
       <c r="C61" s="1">
-        <v>21.77</v>
+        <v>14.25</v>
       </c>
       <c r="D61" s="1">
-        <v>21.59</v>
+        <v>14.12</v>
       </c>
       <c r="E61" s="1">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="F61" t="s">
-        <v>14</v>
+        <v>126</v>
       </c>
       <c r="G61" s="1">
-        <v>21.59</v>
+        <v>14.12</v>
       </c>
       <c r="H61" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>133</v>
-      </c>
-      <c r="B62" t="s">
-        <v>134</v>
-      </c>
-      <c r="C62" s="1">
-        <v>9.79</v>
-      </c>
-      <c r="D62" s="1">
-        <v>9.65</v>
-      </c>
-      <c r="E62" s="1">
-        <v>0.14</v>
-      </c>
-      <c r="F62" t="s">
-        <v>126</v>
-      </c>
-      <c r="G62" s="1">
-        <v>9.65</v>
-      </c>
-      <c r="H62" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>135</v>
-      </c>
-      <c r="B63" t="s">
-        <v>136</v>
-      </c>
-      <c r="C63" s="1">
-        <v>14.25</v>
-      </c>
-      <c r="D63" s="1">
-        <v>14.12</v>
-      </c>
-      <c r="E63" s="1">
-        <v>0.13</v>
-      </c>
-      <c r="F63" t="s">
-        <v>126</v>
-      </c>
-      <c r="G63" s="1">
-        <v>14.12</v>
-      </c>
-      <c r="H63" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>137</v>
-      </c>
-      <c r="B64" t="s">
-        <v>138</v>
-      </c>
-      <c r="C64" s="1">
-        <v>12.55</v>
-      </c>
-      <c r="D64" s="1">
-        <v>12.49</v>
-      </c>
-      <c r="E64" s="1">
-        <v>0.06</v>
-      </c>
-      <c r="F64" t="s">
-        <v>14</v>
-      </c>
-      <c r="G64" s="1">
-        <v>12.49</v>
-      </c>
-      <c r="H64" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>139</v>
-      </c>
-      <c r="B65" t="s">
-        <v>140</v>
-      </c>
-      <c r="C65" s="1">
-        <v>14.9</v>
-      </c>
-      <c r="D65" s="1">
-        <v>14.85</v>
-      </c>
-      <c r="E65" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="F65" t="s">
-        <v>14</v>
-      </c>
-      <c r="G65" s="1">
-        <v>14.85</v>
-      </c>
-      <c r="H65" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>141</v>
-      </c>
-      <c r="B66" t="s">
-        <v>142</v>
-      </c>
-      <c r="C66" s="1">
-        <v>12.29</v>
-      </c>
-      <c r="D66" s="1">
-        <v>12.27</v>
-      </c>
-      <c r="E66" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="F66" t="s">
-        <v>14</v>
-      </c>
-      <c r="G66" s="1">
-        <v>12.27</v>
-      </c>
-      <c r="H66" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>143</v>
-      </c>
-      <c r="B67" t="s">
-        <v>144</v>
-      </c>
-      <c r="C67" s="1">
-        <v>12.19</v>
-      </c>
-      <c r="D67" s="1">
-        <v>12.18</v>
-      </c>
-      <c r="E67" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="F67" t="s">
-        <v>14</v>
-      </c>
-      <c r="G67" s="1">
-        <v>12.18</v>
-      </c>
-      <c r="H67" t="s">
         <v>11</v>
       </c>
     </row>
